--- a/feedback_surveys/023_smart_building_dashboard_experience_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/023_smart_building_dashboard_experience_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dashboard Usage</t>
+          <t>How do you typically use the dashboard?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>overall_satisfaction</t>
+          <t>Overall Satisfaction</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,14 +571,10 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>issue_satisfaction</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>How satisfied are you with the current state of our building dashboard?</t>
-        </is>
-      </c>
+          <t>Satisfaction with Current State</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -598,14 +594,10 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>feature_requests</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>What features would you like to see added to the dashboard?</t>
-        </is>
-      </c>
+          <t>Feature Requests</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -625,14 +617,10 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>issue_description</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Please describe any issues you have with the current state of our building dashboard.</t>
-        </is>
-      </c>
+          <t>Description of Issues</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -647,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>issue_urgent</t>
+          <t>issue_urgency</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>urgent</t>
+          <t>Urgency</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -675,13 +663,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>issue_priority</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -698,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>issue_frequency</t>
+          <t>Frequency of Issues</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -721,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>issue_category</t>
+          <t>Issue Category</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -744,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>issue_resolution</t>
+          <t>Can be Resolved</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -762,58 +750,58 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>feedback_urgent</t>
+          <t>feedback_urgency</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>urgent</t>
+          <t>Urgency of Feedback</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>feedback_priority</t>
+          <t>feedback_frequency</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>priority</t>
+          <t>Frequency of Feedback</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>feedback_frequency</t>
+          <t>feedback_category</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>feedback_frequency</t>
+          <t>Feedback Category</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -826,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>feedback_category</t>
+          <t>feedback_comments</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>feedback_category</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -854,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>feedback_comments</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Email Address</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -877,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>issue_comments</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -900,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>feature_requests_comments</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -918,17 +906,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>feedback_urgency_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Urgency of Feedback Needed</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -941,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>feedback_frequency_urgency</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Frequency of Feedback Needed</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -969,131 +957,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>feature_requests_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Feature Requests 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>feedback_urgency</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>urgency</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>feedback_frequency_urgency</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>frequency_urgency</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>feature_requests</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>feature_requests</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1110,7 +983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1143,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1160,46 +1033,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>issue_satisfaction_choices</t>
+          <t>dashboard_usage_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Very Dissatisfied</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>issue_satisfaction_choices</t>
+          <t>dashboard_usage_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>somewhat_dissatisfied</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Somewhat Dissatisfied</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Somewhat Satisfied</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1245,80 +1118,80 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Very Satisfied</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>issue_urgent_choices</t>
+          <t>issue_satisfaction_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>urgent</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Urgent</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>issue_urgent_choices</t>
+          <t>issue_satisfaction_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_urgent</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Not Urgent</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>issue_priority_choices</t>
+          <t>issue_urgency_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>urgent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Urgent</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>issue_priority_choices</t>
+          <t>issue_urgency_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>not_urgent</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Not Urgent</t>
         </is>
       </c>
     </row>
@@ -1330,53 +1203,53 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>issue_frequency_choices</t>
+          <t>issue_priority_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>issue_frequency_choices</t>
+          <t>issue_priority_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>issue_category_choices</t>
+          <t>issue_frequency_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1393,7 +1266,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>issue_category_choices</t>
+          <t>issue_frequency_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1410,119 +1283,119 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>issue_resolution_choices</t>
+          <t>issue_category_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>issue_resolution_choices</t>
+          <t>issue_category_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>feedback_urgent_choices</t>
+          <t>issue_resolution_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>urgent</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Urgent</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>feedback_urgent_choices</t>
+          <t>issue_resolution_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_urgent</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Not Urgent</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>feedback_priority_choices</t>
+          <t>feedback_urgency_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>urgent</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Urgent</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>feedback_priority_choices</t>
+          <t>feedback_urgency_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>not_urgent</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Not Urgent</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>feedback_priority_choices</t>
+          <t>feedback_frequency_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1534,29 +1407,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>feedback_frequency_choices</t>
+          <t>feedback_category_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1568,63 +1441,63 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>feedback_category_choices</t>
+          <t>feedback_urgency_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>feedback_urgency_choices</t>
+          <t>feedback_urgency_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>feedback_urgency_choices</t>
+          <t>feedback_frequency_urgency_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1636,27 +1509,10 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>feedback_frequency_urgency_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
         <is>
           <t>No</t>
         </is>
